--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.31310915232086</v>
+        <v>7.525880237252141</v>
       </c>
       <c r="D2" t="n">
-        <v>8.833375404320748</v>
+        <v>1.435423503202122</v>
       </c>
       <c r="E2" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F2" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.42053641019355</v>
+        <v>6.243337166656452</v>
       </c>
       <c r="D3" t="n">
-        <v>17.81510748268486</v>
+        <v>2.89495496593629</v>
       </c>
       <c r="E3" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F3" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.90280700908978</v>
+        <v>4.696706138977089</v>
       </c>
       <c r="D4" t="n">
-        <v>29.03079787911049</v>
+        <v>4.717504655355455</v>
       </c>
       <c r="E4" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F4" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.31228439285148</v>
+        <v>7.200746213838366</v>
       </c>
       <c r="D5" t="n">
-        <v>17.48964398164612</v>
+        <v>2.842067147017494</v>
       </c>
       <c r="E5" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F5" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.74374809959914</v>
+        <v>5.64585906618486</v>
       </c>
       <c r="D6" t="n">
-        <v>13.73940110646696</v>
+        <v>2.232652679800882</v>
       </c>
       <c r="E6" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F6" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.05224089309343</v>
+        <v>4.558489145127682</v>
       </c>
       <c r="D7" t="n">
-        <v>22.03633298879862</v>
+        <v>3.580904110679775</v>
       </c>
       <c r="E7" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F7" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.98738583151964</v>
+        <v>9.747950197621941</v>
       </c>
       <c r="D8" t="n">
-        <v>60.17849470742748</v>
+        <v>9.779005389956966</v>
       </c>
       <c r="E8" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F8" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.96983369528508</v>
+        <v>4.220097975483825</v>
       </c>
       <c r="D9" t="n">
-        <v>25.79635486854061</v>
+        <v>4.191907666137849</v>
       </c>
       <c r="E9" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F9" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.39658806317575</v>
+        <v>5.26444556026606</v>
       </c>
       <c r="D10" t="n">
-        <v>32.53827034882146</v>
+        <v>5.287468931683486</v>
       </c>
       <c r="E10" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F10" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>53.76516198277038</v>
+        <v>8.736838822200188</v>
       </c>
       <c r="D11" t="n">
-        <v>53.93547131617307</v>
+        <v>8.764514088878125</v>
       </c>
       <c r="E11" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F11" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.67172364794192</v>
+        <v>6.609155092790561</v>
       </c>
       <c r="D12" t="n">
-        <v>40.59456900551088</v>
+        <v>6.596617463395519</v>
       </c>
       <c r="E12" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F12" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.7928323166297</v>
+        <v>4.028835251452326</v>
       </c>
       <c r="D13" t="n">
-        <v>24.66334294947611</v>
+        <v>4.007793229289868</v>
       </c>
       <c r="E13" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F13" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>53.06037240081412</v>
+        <v>8.622310515132295</v>
       </c>
       <c r="D14" t="n">
-        <v>53.21080702865152</v>
+        <v>8.646756142155873</v>
       </c>
       <c r="E14" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F14" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.20193748640938</v>
+        <v>6.207814841541525</v>
       </c>
       <c r="D15" t="n">
-        <v>39.326909478105</v>
+        <v>6.390622790192063</v>
       </c>
       <c r="E15" t="n">
-        <v>10.67667405210993</v>
+        <v>1.734959533467864</v>
       </c>
       <c r="F15" t="n">
-        <v>15.42190344374752</v>
+        <v>2.506059309608971</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
